--- a/data/raw/margin/White Mulberry.xlsx
+++ b/data/raw/margin/White Mulberry.xlsx
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.155</v>
+        <v>0.05</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -6652,13 +6652,13 @@
         <v>183.904232492647</v>
       </c>
       <c r="S46" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="T46" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U46" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="V46" t="n">
         <v>10</v>
@@ -6676,7 +6676,7 @@
         <v>18</v>
       </c>
       <c r="AA46" t="n">
-        <v>129.5084745762712</v>
+        <v>111.2033898305084</v>
       </c>
       <c r="AB46" t="n">
         <v>9.195211624632352</v>
@@ -6688,19 +6688,19 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>849</v>
+        <v>729</v>
       </c>
       <c r="AF46" t="n">
         <v>4499</v>
       </c>
       <c r="AG46" t="n">
-        <v>563.64</v>
+        <v>461.95</v>
       </c>
       <c r="AH46" t="n">
-        <v>66.39</v>
+        <v>63.37</v>
       </c>
       <c r="AI46" t="n">
-        <v>899.9400000000001</v>
+        <v>772.74</v>
       </c>
       <c r="AJ46" t="n">
         <v>849</v>
@@ -6708,16 +6708,16 @@
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
       <c r="AM46" t="n">
-        <v>899.9400000000001</v>
+        <v>772.74</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
       </c>
       <c r="AO46" t="n">
-        <v>176</v>
+        <v>182.85</v>
       </c>
       <c r="AP46" t="n">
-        <v>20.73</v>
+        <v>25.08</v>
       </c>
     </row>
     <row r="47">
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6786,13 +6786,13 @@
         <v>118.0837929938824</v>
       </c>
       <c r="S47" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T47" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="U47" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="V47" t="n">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>76.11864406779659</v>
+        <v>65.4406779661017</v>
       </c>
       <c r="AB47" t="n">
         <v>5.904189649694118</v>
@@ -6822,19 +6822,19 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>499</v>
+        <v>429</v>
       </c>
       <c r="AF47" t="n">
         <v>4499</v>
       </c>
       <c r="AG47" t="n">
-        <v>322.81</v>
+        <v>263.49</v>
       </c>
       <c r="AH47" t="n">
-        <v>64.69</v>
+        <v>61.42</v>
       </c>
       <c r="AI47" t="n">
-        <v>528.9400000000001</v>
+        <v>454.74</v>
       </c>
       <c r="AJ47" t="n">
         <v>499</v>
@@ -6842,16 +6842,16 @@
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="n">
-        <v>528.9400000000001</v>
+        <v>454.74</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
       </c>
       <c r="AO47" t="n">
-        <v>15.7</v>
+        <v>64.66</v>
       </c>
       <c r="AP47" t="n">
-        <v>3.15</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="48">
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.155</v>
+        <v>0.05</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6920,13 +6920,13 @@
         <v>187.4573969405294</v>
       </c>
       <c r="S48" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="T48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U48" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="V48" t="n">
         <v>10</v>
@@ -6944,7 +6944,7 @@
         <v>18</v>
       </c>
       <c r="AA48" t="n">
-        <v>99</v>
+        <v>88.32203389830505</v>
       </c>
       <c r="AB48" t="n">
         <v>9.37286984702647</v>
@@ -6956,19 +6956,19 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>649</v>
+        <v>579</v>
       </c>
       <c r="AF48" t="n">
         <v>4499</v>
       </c>
       <c r="AG48" t="n">
-        <v>391.14</v>
+        <v>331.82</v>
       </c>
       <c r="AH48" t="n">
-        <v>60.27</v>
+        <v>57.31</v>
       </c>
       <c r="AI48" t="n">
-        <v>687.9400000000001</v>
+        <v>613.74</v>
       </c>
       <c r="AJ48" t="n">
         <v>649</v>
@@ -6976,16 +6976,16 @@
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="n">
-        <v>687.9400000000001</v>
+        <v>613.74</v>
       </c>
       <c r="AN48" t="n">
         <v>0</v>
       </c>
       <c r="AO48" t="n">
-        <v>0.22</v>
+        <v>52.44</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.03</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="49">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.155</v>
+        <v>0.05</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7054,13 +7054,13 @@
         <v>221.3913917647058</v>
       </c>
       <c r="S49" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="T49" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U49" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="V49" t="n">
         <v>10</v>
@@ -7078,7 +7078,7 @@
         <v>18</v>
       </c>
       <c r="AA49" t="n">
-        <v>114.2542372881355</v>
+        <v>117.9152542372881</v>
       </c>
       <c r="AB49" t="n">
         <v>11.06956958823529</v>
@@ -7090,19 +7090,19 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>749</v>
+        <v>773</v>
       </c>
       <c r="AF49" t="n">
         <v>4499</v>
       </c>
       <c r="AG49" t="n">
-        <v>447.13</v>
+        <v>467.46</v>
       </c>
       <c r="AH49" t="n">
-        <v>59.7</v>
+        <v>60.47</v>
       </c>
       <c r="AI49" t="n">
-        <v>793.9400000000001</v>
+        <v>819.38</v>
       </c>
       <c r="AJ49" t="n">
         <v>749</v>
@@ -7110,16 +7110,16 @@
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="n">
-        <v>793.9400000000001</v>
+        <v>819.38</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
       </c>
       <c r="AO49" t="n">
-        <v>88.98999999999999</v>
+        <v>137.69</v>
       </c>
       <c r="AP49" t="n">
-        <v>11.88</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="50">
@@ -7191,10 +7191,10 @@
         <v>17</v>
       </c>
       <c r="T50" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U50" t="n">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="V50" t="n">
         <v>10</v>
@@ -7212,7 +7212,7 @@
         <v>18</v>
       </c>
       <c r="AA50" t="n">
-        <v>320.1864406779659</v>
+        <v>343.9830508474574</v>
       </c>
       <c r="AB50" t="n">
         <v>37.85242522939412</v>
@@ -7224,19 +7224,19 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>2099</v>
+        <v>2255</v>
       </c>
       <c r="AF50" t="n">
         <v>4499</v>
       </c>
       <c r="AG50" t="n">
-        <v>1137.25</v>
+        <v>1269.45</v>
       </c>
       <c r="AH50" t="n">
-        <v>54.18</v>
+        <v>56.29</v>
       </c>
       <c r="AI50" t="n">
-        <v>2224.94</v>
+        <v>2390.3</v>
       </c>
       <c r="AJ50" t="n">
         <v>2099</v>
@@ -7244,16 +7244,16 @@
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="n">
-        <v>2224.94</v>
+        <v>2390.3</v>
       </c>
       <c r="AN50" t="n">
         <v>0</v>
       </c>
       <c r="AO50" t="n">
-        <v>95.02</v>
+        <v>214.19</v>
       </c>
       <c r="AP50" t="n">
-        <v>4.53</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="51">
